--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/COLETOR ADMISSAO - 01_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/COLETOR ADMISSAO - 01_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,7 +452,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -478,11 +472,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -503,11 +492,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -528,7 +512,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -549,7 +532,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -566,11 +548,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -591,7 +568,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -612,7 +588,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -633,7 +608,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -654,11 +628,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -679,11 +648,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -704,7 +668,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -725,11 +688,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -746,7 +704,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -763,7 +720,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -784,11 +740,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -809,7 +760,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -830,11 +780,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -855,11 +800,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -880,11 +820,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -905,7 +840,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -926,7 +860,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -943,7 +876,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -964,9 +896,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>10</t>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>070341180259</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>COLETOR ADMISSAO IRON FAZER150/ FACTOR/ XTTZ150 201908</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
